--- a/translations/welsh-translations/multi-year/xlsx/04-accept-single-sonfirm-prn.xlsx
+++ b/translations/welsh-translations/multi-year/xlsx/04-accept-single-sonfirm-prn.xlsx
@@ -81,8 +81,7 @@
     <t>Accept this PERN towards your {0} recycling obligations?</t>
   </si>
   <si>
-    <t xml:space="preserve">Derbyn y PERN yma tuag at eich rhwymedigaethau ailgylchu ar gyfer {0}?
-</t>
+    <t xml:space="preserve">Derbyn y PERN yma tuag at eich rhwymedigaethau ailgylchu ar gyfer {0}?</t>
   </si>
   <si>
     <t>src/FrontendSchemeRegistration.UI/Resources/Views/PrnsAccept/AcceptSinglePrn.en.resx::pern_page_title</t>
